--- a/tests/fixtures/19_blood_pressure_tracker/data-export-control.xlsx
+++ b/tests/fixtures/19_blood_pressure_tracker/data-export-control.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -534,428 +534,429 @@
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>table:</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>HEADER</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>measurement.date</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>measurement.time</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>measurement.systolic</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>measurement.diastolic</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>measurement.heart_rate</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>measurement.comments</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="n"/>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="n">
+    <row r="5">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n">
         <v>39022</v>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Morgens</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F5" s="4" t="n">
         <v>129</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>79</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="I4" s="4" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="n">
+      <c r="I5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n"/>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n">
         <v>39022</v>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Früher Abend</t>
         </is>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="F6" s="7" t="n">
         <v>133</v>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="G6" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="H5" s="7" t="n">
+      <c r="H6" s="7" t="n">
         <v>75</v>
       </c>
-      <c r="I5" s="7" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="I6" s="7" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>39023</v>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Morgens</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F7" s="4" t="n">
         <v>142</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="I6" s="4" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="n">
+      <c r="I7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
         <v>39023</v>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>Früher Abend</t>
         </is>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="F8" s="7" t="n">
         <v>141</v>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="G8" s="7" t="n">
         <v>84</v>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="H8" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="I7" s="7" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n"/>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n">
+      <c r="I8" s="7" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
         <v>39024</v>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Morgens</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F9" s="4" t="n">
         <v>137</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>84</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="I8" s="4" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="n">
+      <c r="I9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n">
         <v>39024</v>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Früher Abend</t>
         </is>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F10" s="7" t="n">
         <v>139</v>
       </c>
-      <c r="G9" s="7" t="n">
+      <c r="G10" s="7" t="n">
         <v>83</v>
       </c>
-      <c r="H9" s="7" t="n">
+      <c r="H10" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="I9" s="7" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n">
+      <c r="I10" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
         <v>39025</v>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Morgens</t>
         </is>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F11" s="4" t="n">
         <v>140</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="I10" s="4" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="n">
+      <c r="I11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
         <v>39025</v>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>Früher Abend</t>
         </is>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F12" s="7" t="n">
         <v>138</v>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="G12" s="7" t="n">
         <v>85</v>
       </c>
-      <c r="H11" s="7" t="n">
+      <c r="H12" s="7" t="n">
         <v>69</v>
       </c>
-      <c r="I11" s="7" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n">
+      <c r="I12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
         <v>39026</v>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Morgens</t>
         </is>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F13" s="4" t="n">
         <v>135</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>79</v>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="I12" s="4" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="n">
+      <c r="I13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n">
         <v>39026</v>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>Früher Abend</t>
         </is>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F14" s="7" t="n">
         <v>136</v>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="G14" s="7" t="n">
         <v>81</v>
       </c>
-      <c r="H13" s="7" t="n">
+      <c r="H14" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="I13" s="7" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="n">
+      <c r="I14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
         <v>39027</v>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Morgens</t>
         </is>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F15" s="4" t="n">
         <v>137</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>83</v>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="I14" s="4" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="n"/>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="n">
+      <c r="I15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
         <v>39027</v>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>Früher Abend</t>
         </is>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="F16" s="7" t="n">
         <v>138</v>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="G16" s="7" t="n">
         <v>85</v>
       </c>
-      <c r="H15" s="7" t="n">
+      <c r="H16" s="7" t="n">
         <v>66</v>
       </c>
-      <c r="I15" s="7" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n"/>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="n">
+      <c r="I16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
         <v>39028</v>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Morgens</t>
         </is>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F17" s="4" t="n">
         <v>135</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="I16" s="4" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="n"/>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="n">
+      <c r="I17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
         <v>39028</v>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>Früher Abend</t>
         </is>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="F18" s="7" t="n">
         <v>142</v>
       </c>
-      <c r="G17" s="7" t="n">
+      <c r="G18" s="7" t="n">
         <v>85</v>
       </c>
-      <c r="H17" s="7" t="n">
+      <c r="H18" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="I17" s="7" t="n"/>
+      <c r="I18" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
